--- a/dataset_t6_grouped/results2/G5/G5_T6165_W0035F0001T0006Z000C1N36_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T6165_W0035F0001T0006Z000C1N36_analysis.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -486,10 +486,10 @@
         <v>11.2084800754855</v>
       </c>
       <c r="E2" t="n">
-        <v>21.55537133710182</v>
+        <v>20.39028226310311</v>
       </c>
       <c r="F2" t="n">
-        <v>25.8262569593567</v>
+        <v>23.97010605084704</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -518,10 +518,10 @@
         <v>10.79356360121272</v>
       </c>
       <c r="E3" t="n">
-        <v>21.55537133710182</v>
+        <v>20.39028226310311</v>
       </c>
       <c r="F3" t="n">
-        <v>25.8262569593567</v>
+        <v>23.97010605084704</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -550,10 +550,10 @@
         <v>65.78560773281193</v>
       </c>
       <c r="E4" t="n">
-        <v>21.55537133710182</v>
+        <v>20.39028226310311</v>
       </c>
       <c r="F4" t="n">
-        <v>25.8262569593567</v>
+        <v>23.97010605084704</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -561,6 +561,38 @@
         </is>
       </c>
       <c r="H4" t="inlineStr">
+        <is>
+          <t>G5</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>W0035F0001T0006Z000C1N36.png</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>4</v>
+      </c>
+      <c r="C5" t="n">
+        <v>7.688053404482408</v>
+      </c>
+      <c r="D5" t="n">
+        <v>9.353514304877047</v>
+      </c>
+      <c r="E5" t="n">
+        <v>20.39028226310311</v>
+      </c>
+      <c r="F5" t="n">
+        <v>23.97010605084704</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>T6165</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
         <is>
           <t>G5</t>
         </is>

--- a/dataset_t6_grouped/results2/G5/G5_T6165_W0035F0001T0006Z000C1N36_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T6165_W0035F0001T0006Z000C1N36_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>10.96474147498489</v>
+        <v>1.781770489685045</v>
       </c>
       <c r="D2" t="n">
-        <v>11.2084800754855</v>
+        <v>1.821378012266395</v>
       </c>
       <c r="E2" t="n">
-        <v>20.39028226310311</v>
+        <v>3.313420867754255</v>
       </c>
       <c r="F2" t="n">
-        <v>23.97010605084704</v>
+        <v>3.895142233262643</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>11.81917641771873</v>
+        <v>1.920616167879294</v>
       </c>
       <c r="D3" t="n">
-        <v>10.79356360121272</v>
+        <v>1.753954085197067</v>
       </c>
       <c r="E3" t="n">
-        <v>20.39028226310311</v>
+        <v>3.313420867754255</v>
       </c>
       <c r="F3" t="n">
-        <v>23.97010605084704</v>
+        <v>3.895142233262643</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>57.11181903316808</v>
+        <v>9.280670592889814</v>
       </c>
       <c r="D4" t="n">
-        <v>65.78560773281193</v>
+        <v>10.69016125658194</v>
       </c>
       <c r="E4" t="n">
-        <v>20.39028226310311</v>
+        <v>3.313420867754255</v>
       </c>
       <c r="F4" t="n">
-        <v>23.97010605084704</v>
+        <v>3.895142233262643</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>7.688053404482408</v>
+        <v>1.249308678228391</v>
       </c>
       <c r="D5" t="n">
-        <v>9.353514304877047</v>
+        <v>1.51994607454252</v>
       </c>
       <c r="E5" t="n">
-        <v>20.39028226310311</v>
+        <v>3.313420867754255</v>
       </c>
       <c r="F5" t="n">
-        <v>23.97010605084704</v>
+        <v>3.895142233262643</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
